--- a/data/derived_data/2_RarefyData/Dataset_1/ps_rare_ITS_D1bis_tax_table.xlsx
+++ b/data/derived_data/2_RarefyData/Dataset_1/ps_rare_ITS_D1bis_tax_table.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t xml:space="preserve">Cluster_113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pulcherrima</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_116</t>
@@ -675,22 +678,22 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
         <v>22</v>
@@ -727,30 +730,30 @@
         <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
@@ -771,12 +774,12 @@
         <v>19</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -797,12 +800,12 @@
         <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
         <v>9</v>
@@ -823,12 +826,12 @@
         <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
         <v>9</v>
@@ -849,12 +852,12 @@
         <v>19</v>
       </c>
       <c r="H10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
         <v>9</v>
@@ -875,12 +878,12 @@
         <v>19</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
         <v>9</v>
@@ -906,7 +909,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
@@ -915,16 +918,16 @@
         <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H13" t="s">
         <v>22</v>
@@ -932,7 +935,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
         <v>9</v>
@@ -958,7 +961,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
         <v>9</v>
@@ -979,12 +982,12 @@
         <v>19</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
         <v>9</v>
@@ -993,16 +996,16 @@
         <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H16" t="s">
         <v>22</v>
@@ -1010,7 +1013,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
         <v>9</v>
@@ -1036,7 +1039,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -1062,7 +1065,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
         <v>9</v>
@@ -1088,7 +1091,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
@@ -1109,12 +1112,12 @@
         <v>19</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
         <v>9</v>
@@ -1135,12 +1138,12 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
         <v>9</v>
@@ -1161,12 +1164,12 @@
         <v>19</v>
       </c>
       <c r="H22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
         <v>9</v>
@@ -1187,12 +1190,12 @@
         <v>19</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
         <v>9</v>
@@ -1213,12 +1216,12 @@
         <v>19</v>
       </c>
       <c r="H24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
@@ -1239,12 +1242,12 @@
         <v>19</v>
       </c>
       <c r="H25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B26" t="s">
         <v>9</v>
@@ -1265,12 +1268,12 @@
         <v>19</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
         <v>9</v>
@@ -1291,12 +1294,12 @@
         <v>19</v>
       </c>
       <c r="H27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
         <v>9</v>
@@ -1305,13 +1308,13 @@
         <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G28" t="s">
         <v>22</v>
@@ -1322,7 +1325,7 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B29" t="s">
         <v>9</v>
@@ -1343,12 +1346,12 @@
         <v>19</v>
       </c>
       <c r="H29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
         <v>9</v>
@@ -1357,16 +1360,16 @@
         <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E30" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G30" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H30" t="s">
         <v>22</v>
@@ -1374,7 +1377,7 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
         <v>9</v>
@@ -1395,12 +1398,12 @@
         <v>19</v>
       </c>
       <c r="H31" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
@@ -1421,12 +1424,12 @@
         <v>19</v>
       </c>
       <c r="H32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" t="s">
         <v>9</v>
@@ -1452,25 +1455,25 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F34" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G34" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H34" t="s">
         <v>22</v>
@@ -1478,7 +1481,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
         <v>9</v>
@@ -1499,12 +1502,12 @@
         <v>19</v>
       </c>
       <c r="H35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B36" t="s">
         <v>9</v>
@@ -1525,12 +1528,12 @@
         <v>19</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
         <v>9</v>
@@ -1539,16 +1542,16 @@
         <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E37" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H37" t="s">
         <v>22</v>
@@ -1556,25 +1559,25 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F38" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G38" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H38" t="s">
         <v>22</v>
@@ -1582,7 +1585,7 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B39" t="s">
         <v>9</v>
@@ -1603,12 +1606,12 @@
         <v>19</v>
       </c>
       <c r="H39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B40" t="s">
         <v>9</v>
@@ -1629,12 +1632,12 @@
         <v>19</v>
       </c>
       <c r="H40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
         <v>9</v>
@@ -1655,30 +1658,30 @@
         <v>19</v>
       </c>
       <c r="H41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F42" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G42" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H42" t="s">
         <v>22</v>
@@ -1686,25 +1689,25 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D43" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E43" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F43" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G43" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H43" t="s">
         <v>22</v>
@@ -1712,7 +1715,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
@@ -1733,38 +1736,38 @@
         <v>19</v>
       </c>
       <c r="H44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E45" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F45" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G45" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H45" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B46" t="s">
         <v>9</v>
@@ -1785,7 +1788,7 @@
         <v>19</v>
       </c>
       <c r="H46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
